--- a/BD_Presupuesto_EDT.xlsx
+++ b/BD_Presupuesto_EDT.xlsx
@@ -1,41 +1,520 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desarrollo de Proyectos\Reporte Diario tiempo real\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D51C2FB9-FE0B-4484-AABB-A592A0F642FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Presupuesto" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="161">
+  <si>
+    <t>edt_id</t>
+  </si>
+  <si>
+    <t>edt_nombre</t>
+  </si>
+  <si>
+    <t>actividad_id</t>
+  </si>
+  <si>
+    <t>actividad_nombre</t>
+  </si>
+  <si>
+    <t>codigo</t>
+  </si>
+  <si>
+    <t>unidad</t>
+  </si>
+  <si>
+    <t>metrado_total_planificado</t>
+  </si>
+  <si>
+    <t>precio_unitario</t>
+  </si>
+  <si>
+    <t>precio_parcial</t>
+  </si>
+  <si>
+    <t>presupuesto_total</t>
+  </si>
+  <si>
+    <t>fecha_inicio</t>
+  </si>
+  <si>
+    <t>fecha_fin</t>
+  </si>
+  <si>
+    <t>nivel_wbs</t>
+  </si>
+  <si>
+    <t>padre_id</t>
+  </si>
+  <si>
+    <t>Obras Preliminares y Provisionales</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>OBR-PRE</t>
+  </si>
+  <si>
+    <t>Global</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>Limpieza de terreno manual</t>
+  </si>
+  <si>
+    <t>OBR-PRE-01</t>
+  </si>
+  <si>
+    <t>m2</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>Trazo, nivelación y replanteo de zapatas</t>
+  </si>
+  <si>
+    <t>OBR-PRE-02</t>
+  </si>
+  <si>
+    <t>2026-06-02</t>
+  </si>
+  <si>
+    <t>2026-06-07</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>Cerco provisional de obra con madera</t>
+  </si>
+  <si>
+    <t>OBR-PRE-03</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>1.4</t>
+  </si>
+  <si>
+    <t>Construcción de almacén y oficina provisional</t>
+  </si>
+  <si>
+    <t>OBR-PRE-04</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>Movimiento de Tierras</t>
+  </si>
+  <si>
+    <t>MOV-TIE</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>Excavación masiva con excavadora</t>
+  </si>
+  <si>
+    <t>MOV-TIE-01</t>
+  </si>
+  <si>
+    <t>m3</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>2.2</t>
+  </si>
+  <si>
+    <t>Excavación manual de zanjas y vigas cimentación</t>
+  </si>
+  <si>
+    <t>MOV-TIE-02</t>
+  </si>
+  <si>
+    <t>2026-06-15</t>
+  </si>
+  <si>
+    <t>2.3</t>
+  </si>
+  <si>
+    <t>Relleno y compactado con vibradora</t>
+  </si>
+  <si>
+    <t>MOV-TIE-03</t>
+  </si>
+  <si>
+    <t>2026-06-18</t>
+  </si>
+  <si>
+    <t>2.4</t>
+  </si>
+  <si>
+    <t>Eliminación de desmonte c/volquete 15m3</t>
+  </si>
+  <si>
+    <t>MOV-TIE-04</t>
+  </si>
+  <si>
+    <t>2026-06-06</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>Estructuras de Concreto</t>
+  </si>
+  <si>
+    <t>EST-CON</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>Solado de concreto e=3" f'c=100 kg/cm2</t>
+  </si>
+  <si>
+    <t>EST-CON-01</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>Concreto f'c=210 kg/cm2 premezclado zapatas</t>
+  </si>
+  <si>
+    <t>EST-CON-02</t>
+  </si>
+  <si>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>3.3</t>
+  </si>
+  <si>
+    <t>Acero de refuerzo corrugado fy=4200 en zapatas</t>
+  </si>
+  <si>
+    <t>EST-CON-03</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>2026-06-16</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
+  </si>
+  <si>
+    <t>3.4</t>
+  </si>
+  <si>
+    <t>Concreto f'c=280 kg/cm2 en columnas</t>
+  </si>
+  <si>
+    <t>EST-CON-04</t>
+  </si>
+  <si>
+    <t>2026-06-25</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>Encofrado y desencofrado metálico columnas</t>
+  </si>
+  <si>
+    <t>EST-CON-05</t>
+  </si>
+  <si>
+    <t>2026-06-22</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>3.6</t>
+  </si>
+  <si>
+    <t>Acero de refuerzo corrugado en columnas</t>
+  </si>
+  <si>
+    <t>EST-CON-06</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>3.7</t>
+  </si>
+  <si>
+    <t>Concreto f'c=210 kg/cm2 en losas y vigas</t>
+  </si>
+  <si>
+    <t>EST-CON-07</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t>Encofrado y desencofrado de vigas y losas</t>
+  </si>
+  <si>
+    <t>EST-CON-08</t>
+  </si>
+  <si>
+    <t>2026-07-05</t>
+  </si>
+  <si>
+    <t>2026-07-26</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>Acero de refuerzo en vigas y losas aligeradas</t>
+  </si>
+  <si>
+    <t>EST-CON-09</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>Arquitectura y Acabados</t>
+  </si>
+  <si>
+    <t>ARQ-ACAB</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>Muros de ladrillo King Kong arcilla cocida</t>
+  </si>
+  <si>
+    <t>ARQ-ACAB-01</t>
+  </si>
+  <si>
+    <t>2026-07-15</t>
+  </si>
+  <si>
+    <t>2026-08-05</t>
+  </si>
+  <si>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>Tarrajeo frotachado de muros interiores</t>
+  </si>
+  <si>
+    <t>ARQ-ACAB-02</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>Tarrajeo fino en cielorrasos y vigas</t>
+  </si>
+  <si>
+    <t>ARQ-ACAB-03</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
+    <t>2026-08-15</t>
+  </si>
+  <si>
+    <t>4.4</t>
+  </si>
+  <si>
+    <t>Contrapiso de concreto e=2" en ambientes</t>
+  </si>
+  <si>
+    <t>ARQ-ACAB-04</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>Instalación de piso porcelanato pulido 60x60</t>
+  </si>
+  <si>
+    <t>ARQ-ACAB-05</t>
+  </si>
+  <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>2026-08-22</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>Pintura látex en muros interiores y columnas</t>
+  </si>
+  <si>
+    <t>ARQ-ACAB-06</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>2026-08-25</t>
+  </si>
+  <si>
+    <t>4.7</t>
+  </si>
+  <si>
+    <t>Puertas de madera contraplacada con cerraduras</t>
+  </si>
+  <si>
+    <t>ARQ-ACAB-07</t>
+  </si>
+  <si>
+    <t>und</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>Ventanas de vidrio templado templado e=8mm</t>
+  </si>
+  <si>
+    <t>ARQ-ACAB-08</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>Instalaciones Sanitarias y Eléctricas</t>
+  </si>
+  <si>
+    <t>INS-SAN</t>
+  </si>
+  <si>
+    <t>5.1</t>
+  </si>
+  <si>
+    <t>Redes de desagüe y ventilación PVC de 4"</t>
+  </si>
+  <si>
+    <t>INS-SAN-01</t>
+  </si>
+  <si>
+    <t>5.2</t>
+  </si>
+  <si>
+    <t>Tendido de tubería de agua fría y caliente PVC</t>
+  </si>
+  <si>
+    <t>INS-SAN-02</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>5.3</t>
+  </si>
+  <si>
+    <t>Tuberías PVC de luz empotradas en losa/muros</t>
+  </si>
+  <si>
+    <t>INS-SAN-03</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
+    <t>Cableado eléctrico de cobre tipo NH-80</t>
+  </si>
+  <si>
+    <t>INS-SAN-04</t>
+  </si>
+  <si>
+    <t>5.5</t>
+  </si>
+  <si>
+    <t>Montaje de aparatos sanitarios y grifería</t>
+  </si>
+  <si>
+    <t>INS-SAN-05</t>
+  </si>
+  <si>
+    <t>jgo</t>
+  </si>
+  <si>
+    <t>2026-08-29</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -72,6 +551,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,115 +883,119 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="42.59765625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>edt_id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>edt_nombre</v>
-      </c>
-      <c r="C1" t="str">
-        <v>actividad_id</v>
-      </c>
-      <c r="D1" t="str">
-        <v>actividad_nombre</v>
-      </c>
-      <c r="E1" t="str">
-        <v>codigo</v>
-      </c>
-      <c r="F1" t="str">
-        <v>unidad</v>
-      </c>
-      <c r="G1" t="str">
-        <v>metrado_total_planificado</v>
-      </c>
-      <c r="H1" t="str">
-        <v>precio_unitario</v>
-      </c>
-      <c r="I1" t="str">
-        <v>precio_parcial</v>
-      </c>
-      <c r="J1" t="str">
-        <v>presupuesto_total</v>
-      </c>
-      <c r="K1" t="str">
-        <v>fecha_inicio</v>
-      </c>
-      <c r="L1" t="str">
-        <v>fecha_fin</v>
-      </c>
-      <c r="M1" t="str">
-        <v>nivel_wbs</v>
-      </c>
-      <c r="N1" t="str">
-        <v>padre_id</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>Obras Preliminares y Provisionales</v>
-      </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v>OBR-PRE</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Global</v>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
-        <v/>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
       </c>
       <c r="J2">
         <v>45000</v>
       </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
-      <c r="L2" t="str">
-        <v/>
+      <c r="K2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L2" t="s">
+        <v>15</v>
       </c>
       <c r="M2">
         <v>1</v>
       </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
+      <c r="N2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v>1.1</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Limpieza de terreno manual</v>
-      </c>
-      <c r="E3" t="str">
-        <v>OBR-PRE-01</v>
-      </c>
-      <c r="F3" t="str">
-        <v>m2</v>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
       </c>
       <c r="G3">
         <v>1500</v>
@@ -518,11 +1009,11 @@
       <c r="J3">
         <v>9000</v>
       </c>
-      <c r="K3" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="L3" t="str">
-        <v>2026-06-05</v>
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
       </c>
       <c r="M3">
         <v>2</v>
@@ -531,24 +1022,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="str">
-        <v/>
-      </c>
-      <c r="C4" t="str">
-        <v>1.2</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Trazo, nivelación y replanteo de zapatas</v>
-      </c>
-      <c r="E4" t="str">
-        <v>OBR-PRE-02</v>
-      </c>
-      <c r="F4" t="str">
-        <v>m2</v>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>21</v>
       </c>
       <c r="G4">
         <v>1500</v>
@@ -562,11 +1053,11 @@
       <c r="J4">
         <v>12000</v>
       </c>
-      <c r="K4" t="str">
-        <v>2026-06-02</v>
-      </c>
-      <c r="L4" t="str">
-        <v>2026-06-07</v>
+      <c r="K4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" t="s">
+        <v>28</v>
       </c>
       <c r="M4">
         <v>2</v>
@@ -575,24 +1066,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="str">
-        <v/>
-      </c>
-      <c r="C5" t="str">
-        <v>1.3</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Cerco provisional de obra con madera</v>
-      </c>
-      <c r="E5" t="str">
-        <v>OBR-PRE-03</v>
-      </c>
-      <c r="F5" t="str">
-        <v>m</v>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
       </c>
       <c r="G5">
         <v>240</v>
@@ -606,11 +1097,11 @@
       <c r="J5">
         <v>12000</v>
       </c>
-      <c r="K5" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="L5" t="str">
-        <v>2026-06-08</v>
+      <c r="K5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" t="s">
+        <v>33</v>
       </c>
       <c r="M5">
         <v>2</v>
@@ -619,24 +1110,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="str">
-        <v/>
-      </c>
-      <c r="C6" t="str">
-        <v>1.4</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Construcción de almacén y oficina provisional</v>
-      </c>
-      <c r="E6" t="str">
-        <v>OBR-PRE-04</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Global</v>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" t="s">
+        <v>17</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -650,11 +1141,11 @@
       <c r="J6">
         <v>12000</v>
       </c>
-      <c r="K6" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="L6" t="str">
-        <v>2026-06-10</v>
+      <c r="K6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" t="s">
+        <v>37</v>
       </c>
       <c r="M6">
         <v>2</v>
@@ -663,68 +1154,68 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="str">
-        <v>Movimiento de Tierras</v>
-      </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7" t="str">
-        <v/>
-      </c>
-      <c r="E7" t="str">
-        <v>MOV-TIE</v>
-      </c>
-      <c r="F7" t="str">
-        <v>Global</v>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v/>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" t="s">
+        <v>15</v>
       </c>
       <c r="J7">
         <v>92250</v>
       </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v/>
+      <c r="K7" t="s">
+        <v>15</v>
+      </c>
+      <c r="L7" t="s">
+        <v>15</v>
       </c>
       <c r="M7">
         <v>1</v>
       </c>
-      <c r="N7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
+      <c r="N7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="str">
-        <v/>
-      </c>
-      <c r="C8" t="str">
-        <v>2.1</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Excavación masiva con excavadora</v>
-      </c>
-      <c r="E8" t="str">
-        <v>MOV-TIE-01</v>
-      </c>
-      <c r="F8" t="str">
-        <v>m3</v>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" t="s">
+        <v>43</v>
       </c>
       <c r="G8">
         <v>1200</v>
@@ -738,11 +1229,11 @@
       <c r="J8">
         <v>26400</v>
       </c>
-      <c r="K8" t="str">
-        <v>2026-06-05</v>
-      </c>
-      <c r="L8" t="str">
-        <v>2026-06-12</v>
+      <c r="K8" t="s">
+        <v>23</v>
+      </c>
+      <c r="L8" t="s">
+        <v>44</v>
       </c>
       <c r="M8">
         <v>2</v>
@@ -751,24 +1242,24 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="str">
-        <v/>
-      </c>
-      <c r="C9" t="str">
-        <v>2.2</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Excavación manual de zanjas y vigas cimentación</v>
-      </c>
-      <c r="E9" t="str">
-        <v>MOV-TIE-02</v>
-      </c>
-      <c r="F9" t="str">
-        <v>m3</v>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" t="s">
+        <v>43</v>
       </c>
       <c r="G9">
         <v>180</v>
@@ -782,11 +1273,11 @@
       <c r="J9">
         <v>8100</v>
       </c>
-      <c r="K9" t="str">
-        <v>2026-06-07</v>
-      </c>
-      <c r="L9" t="str">
-        <v>2026-06-15</v>
+      <c r="K9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L9" t="s">
+        <v>48</v>
       </c>
       <c r="M9">
         <v>2</v>
@@ -795,24 +1286,24 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="str">
-        <v/>
-      </c>
-      <c r="C10" t="str">
-        <v>2.3</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Relleno y compactado con vibradora</v>
-      </c>
-      <c r="E10" t="str">
-        <v>MOV-TIE-03</v>
-      </c>
-      <c r="F10" t="str">
-        <v>m3</v>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F10" t="s">
+        <v>43</v>
       </c>
       <c r="G10">
         <v>450</v>
@@ -826,11 +1317,11 @@
       <c r="J10">
         <v>15750</v>
       </c>
-      <c r="K10" t="str">
-        <v>2026-06-10</v>
-      </c>
-      <c r="L10" t="str">
-        <v>2026-06-18</v>
+      <c r="K10" t="s">
+        <v>37</v>
+      </c>
+      <c r="L10" t="s">
+        <v>52</v>
       </c>
       <c r="M10">
         <v>2</v>
@@ -839,24 +1330,24 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="str">
-        <v/>
-      </c>
-      <c r="C11" t="str">
-        <v>2.4</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Eliminación de desmonte c/volquete 15m3</v>
-      </c>
-      <c r="E11" t="str">
-        <v>MOV-TIE-04</v>
-      </c>
-      <c r="F11" t="str">
-        <v>m3</v>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" t="s">
+        <v>43</v>
       </c>
       <c r="G11">
         <v>1500</v>
@@ -870,11 +1361,11 @@
       <c r="J11">
         <v>42000</v>
       </c>
-      <c r="K11" t="str">
-        <v>2026-06-06</v>
-      </c>
-      <c r="L11" t="str">
-        <v>2026-06-20</v>
+      <c r="K11" t="s">
+        <v>56</v>
+      </c>
+      <c r="L11" t="s">
+        <v>57</v>
       </c>
       <c r="M11">
         <v>2</v>
@@ -883,68 +1374,68 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="str">
-        <v>Estructuras de Concreto</v>
-      </c>
-      <c r="C12" t="str">
-        <v/>
-      </c>
-      <c r="D12" t="str">
-        <v/>
-      </c>
-      <c r="E12" t="str">
-        <v>EST-CON</v>
-      </c>
-      <c r="F12" t="str">
-        <v>Global</v>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v/>
+      <c r="B12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" t="s">
+        <v>15</v>
       </c>
       <c r="J12">
         <v>321350</v>
       </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v/>
+      <c r="K12" t="s">
+        <v>15</v>
+      </c>
+      <c r="L12" t="s">
+        <v>15</v>
       </c>
       <c r="M12">
         <v>1</v>
       </c>
-      <c r="N12" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="13">
+      <c r="N12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="str">
-        <v/>
-      </c>
-      <c r="C13" t="str">
-        <v>3.1</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Solado de concreto e=3" f'c=100 kg/cm2</v>
-      </c>
-      <c r="E13" t="str">
-        <v>EST-CON-01</v>
-      </c>
-      <c r="F13" t="str">
-        <v>m2</v>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13" t="s">
+        <v>62</v>
+      </c>
+      <c r="F13" t="s">
+        <v>21</v>
       </c>
       <c r="G13">
         <v>350</v>
@@ -958,11 +1449,11 @@
       <c r="J13">
         <v>11200</v>
       </c>
-      <c r="K13" t="str">
-        <v>2026-06-15</v>
-      </c>
-      <c r="L13" t="str">
-        <v>2026-06-20</v>
+      <c r="K13" t="s">
+        <v>48</v>
+      </c>
+      <c r="L13" t="s">
+        <v>57</v>
       </c>
       <c r="M13">
         <v>2</v>
@@ -971,24 +1462,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="str">
-        <v/>
-      </c>
-      <c r="C14" t="str">
-        <v>3.2</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Concreto f'c=210 kg/cm2 premezclado zapatas</v>
-      </c>
-      <c r="E14" t="str">
-        <v>EST-CON-02</v>
-      </c>
-      <c r="F14" t="str">
-        <v>m3</v>
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" t="s">
+        <v>65</v>
+      </c>
+      <c r="F14" t="s">
+        <v>43</v>
       </c>
       <c r="G14">
         <v>160</v>
@@ -1002,11 +1493,11 @@
       <c r="J14">
         <v>60800</v>
       </c>
-      <c r="K14" t="str">
-        <v>2026-06-18</v>
-      </c>
-      <c r="L14" t="str">
-        <v>2026-06-26</v>
+      <c r="K14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L14" t="s">
+        <v>66</v>
       </c>
       <c r="M14">
         <v>2</v>
@@ -1015,24 +1506,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="str">
-        <v/>
-      </c>
-      <c r="C15" t="str">
-        <v>3.3</v>
-      </c>
-      <c r="D15" t="str">
-        <v>Acero de refuerzo corrugado fy=4200 en zapatas</v>
-      </c>
-      <c r="E15" t="str">
-        <v>EST-CON-03</v>
-      </c>
-      <c r="F15" t="str">
-        <v>kg</v>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" t="s">
+        <v>70</v>
       </c>
       <c r="G15">
         <v>4500</v>
@@ -1046,11 +1537,11 @@
       <c r="J15">
         <v>24750</v>
       </c>
-      <c r="K15" t="str">
-        <v>2026-06-16</v>
-      </c>
-      <c r="L15" t="str">
-        <v>2026-06-24</v>
+      <c r="K15" t="s">
+        <v>71</v>
+      </c>
+      <c r="L15" t="s">
+        <v>72</v>
       </c>
       <c r="M15">
         <v>2</v>
@@ -1059,24 +1550,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="str">
-        <v/>
-      </c>
-      <c r="C16" t="str">
-        <v>3.4</v>
-      </c>
-      <c r="D16" t="str">
-        <v>Concreto f'c=280 kg/cm2 en columnas</v>
-      </c>
-      <c r="E16" t="str">
-        <v>EST-CON-04</v>
-      </c>
-      <c r="F16" t="str">
-        <v>m3</v>
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16" t="s">
+        <v>43</v>
       </c>
       <c r="G16">
         <v>85</v>
@@ -1090,11 +1581,11 @@
       <c r="J16">
         <v>35700</v>
       </c>
-      <c r="K16" t="str">
-        <v>2026-06-25</v>
-      </c>
-      <c r="L16" t="str">
-        <v>2026-07-10</v>
+      <c r="K16" t="s">
+        <v>76</v>
+      </c>
+      <c r="L16" t="s">
+        <v>77</v>
       </c>
       <c r="M16">
         <v>2</v>
@@ -1103,24 +1594,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="str">
-        <v/>
-      </c>
-      <c r="C17" t="str">
-        <v>3.5</v>
-      </c>
-      <c r="D17" t="str">
-        <v>Encofrado y desencofrado metálico columnas</v>
-      </c>
-      <c r="E17" t="str">
-        <v>EST-CON-05</v>
-      </c>
-      <c r="F17" t="str">
-        <v>m2</v>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" t="s">
+        <v>79</v>
+      </c>
+      <c r="E17" t="s">
+        <v>80</v>
+      </c>
+      <c r="F17" t="s">
+        <v>21</v>
       </c>
       <c r="G17">
         <v>320</v>
@@ -1134,11 +1625,11 @@
       <c r="J17">
         <v>20800</v>
       </c>
-      <c r="K17" t="str">
-        <v>2026-06-22</v>
-      </c>
-      <c r="L17" t="str">
-        <v>2026-07-08</v>
+      <c r="K17" t="s">
+        <v>81</v>
+      </c>
+      <c r="L17" t="s">
+        <v>82</v>
       </c>
       <c r="M17">
         <v>2</v>
@@ -1147,24 +1638,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="str">
-        <v/>
-      </c>
-      <c r="C18" t="str">
-        <v>3.6</v>
-      </c>
-      <c r="D18" t="str">
-        <v>Acero de refuerzo corrugado en columnas</v>
-      </c>
-      <c r="E18" t="str">
-        <v>EST-CON-06</v>
-      </c>
-      <c r="F18" t="str">
-        <v>kg</v>
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D18" t="s">
+        <v>84</v>
+      </c>
+      <c r="E18" t="s">
+        <v>85</v>
+      </c>
+      <c r="F18" t="s">
+        <v>70</v>
       </c>
       <c r="G18">
         <v>6200</v>
@@ -1178,11 +1669,11 @@
       <c r="J18">
         <v>35960</v>
       </c>
-      <c r="K18" t="str">
-        <v>2026-06-20</v>
-      </c>
-      <c r="L18" t="str">
-        <v>2026-07-06</v>
+      <c r="K18" t="s">
+        <v>57</v>
+      </c>
+      <c r="L18" t="s">
+        <v>86</v>
       </c>
       <c r="M18">
         <v>2</v>
@@ -1191,24 +1682,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="str">
-        <v/>
-      </c>
-      <c r="C19" t="str">
-        <v>3.7</v>
-      </c>
-      <c r="D19" t="str">
-        <v>Concreto f'c=210 kg/cm2 en losas y vigas</v>
-      </c>
-      <c r="E19" t="str">
-        <v>EST-CON-07</v>
-      </c>
-      <c r="F19" t="str">
-        <v>m3</v>
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" t="s">
+        <v>88</v>
+      </c>
+      <c r="E19" t="s">
+        <v>89</v>
+      </c>
+      <c r="F19" t="s">
+        <v>43</v>
       </c>
       <c r="G19">
         <v>120</v>
@@ -1222,11 +1713,11 @@
       <c r="J19">
         <v>49200</v>
       </c>
-      <c r="K19" t="str">
-        <v>2026-07-10</v>
-      </c>
-      <c r="L19" t="str">
-        <v>2026-07-28</v>
+      <c r="K19" t="s">
+        <v>77</v>
+      </c>
+      <c r="L19" t="s">
+        <v>90</v>
       </c>
       <c r="M19">
         <v>2</v>
@@ -1235,24 +1726,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="str">
-        <v/>
-      </c>
-      <c r="C20" t="str">
-        <v>3.8</v>
-      </c>
-      <c r="D20" t="str">
-        <v>Encofrado y desencofrado de vigas y losas</v>
-      </c>
-      <c r="E20" t="str">
-        <v>EST-CON-08</v>
-      </c>
-      <c r="F20" t="str">
-        <v>m2</v>
+      <c r="B20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" t="s">
+        <v>91</v>
+      </c>
+      <c r="D20" t="s">
+        <v>92</v>
+      </c>
+      <c r="E20" t="s">
+        <v>93</v>
+      </c>
+      <c r="F20" t="s">
+        <v>21</v>
       </c>
       <c r="G20">
         <v>580</v>
@@ -1266,11 +1757,11 @@
       <c r="J20">
         <v>31900</v>
       </c>
-      <c r="K20" t="str">
-        <v>2026-07-05</v>
-      </c>
-      <c r="L20" t="str">
-        <v>2026-07-26</v>
+      <c r="K20" t="s">
+        <v>94</v>
+      </c>
+      <c r="L20" t="s">
+        <v>95</v>
       </c>
       <c r="M20">
         <v>2</v>
@@ -1279,24 +1770,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="str">
-        <v/>
-      </c>
-      <c r="C21" t="str">
-        <v>3.9</v>
-      </c>
-      <c r="D21" t="str">
-        <v>Acero de refuerzo en vigas y losas aligeradas</v>
-      </c>
-      <c r="E21" t="str">
-        <v>EST-CON-09</v>
-      </c>
-      <c r="F21" t="str">
-        <v>kg</v>
+      <c r="B21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" t="s">
+        <v>97</v>
+      </c>
+      <c r="E21" t="s">
+        <v>98</v>
+      </c>
+      <c r="F21" t="s">
+        <v>70</v>
       </c>
       <c r="G21">
         <v>8800</v>
@@ -1310,11 +1801,11 @@
       <c r="J21">
         <v>51040</v>
       </c>
-      <c r="K21" t="str">
-        <v>2026-07-08</v>
-      </c>
-      <c r="L21" t="str">
-        <v>2026-07-24</v>
+      <c r="K21" t="s">
+        <v>82</v>
+      </c>
+      <c r="L21" t="s">
+        <v>99</v>
       </c>
       <c r="M21">
         <v>2</v>
@@ -1323,68 +1814,68 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="str">
-        <v>Arquitectura y Acabados</v>
-      </c>
-      <c r="C22" t="str">
-        <v/>
-      </c>
-      <c r="D22" t="str">
-        <v/>
-      </c>
-      <c r="E22" t="str">
-        <v>ARQ-ACAB</v>
-      </c>
-      <c r="F22" t="str">
-        <v>Global</v>
-      </c>
-      <c r="G22" t="str">
-        <v/>
-      </c>
-      <c r="H22" t="str">
-        <v/>
-      </c>
-      <c r="I22" t="str">
-        <v/>
+      <c r="B22" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" t="s">
+        <v>101</v>
+      </c>
+      <c r="F22" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" t="s">
+        <v>15</v>
       </c>
       <c r="J22">
         <v>313200</v>
       </c>
-      <c r="K22" t="str">
-        <v/>
-      </c>
-      <c r="L22" t="str">
-        <v/>
+      <c r="K22" t="s">
+        <v>15</v>
+      </c>
+      <c r="L22" t="s">
+        <v>15</v>
       </c>
       <c r="M22">
         <v>1</v>
       </c>
-      <c r="N22" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="23">
+      <c r="N22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="str">
-        <v/>
-      </c>
-      <c r="C23" t="str">
-        <v>4.1</v>
-      </c>
-      <c r="D23" t="str">
-        <v>Muros de ladrillo King Kong arcilla cocida</v>
-      </c>
-      <c r="E23" t="str">
-        <v>ARQ-ACAB-01</v>
-      </c>
-      <c r="F23" t="str">
-        <v>m2</v>
+      <c r="B23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" t="s">
+        <v>102</v>
+      </c>
+      <c r="D23" t="s">
+        <v>103</v>
+      </c>
+      <c r="E23" t="s">
+        <v>104</v>
+      </c>
+      <c r="F23" t="s">
+        <v>21</v>
       </c>
       <c r="G23">
         <v>1100</v>
@@ -1398,11 +1889,11 @@
       <c r="J23">
         <v>82500</v>
       </c>
-      <c r="K23" t="str">
-        <v>2026-07-15</v>
-      </c>
-      <c r="L23" t="str">
-        <v>2026-08-05</v>
+      <c r="K23" t="s">
+        <v>105</v>
+      </c>
+      <c r="L23" t="s">
+        <v>106</v>
       </c>
       <c r="M23">
         <v>2</v>
@@ -1411,24 +1902,24 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="str">
-        <v/>
-      </c>
-      <c r="C24" t="str">
-        <v>4.2</v>
-      </c>
-      <c r="D24" t="str">
-        <v>Tarrajeo frotachado de muros interiores</v>
-      </c>
-      <c r="E24" t="str">
-        <v>ARQ-ACAB-02</v>
-      </c>
-      <c r="F24" t="str">
-        <v>m2</v>
+      <c r="B24" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" t="s">
+        <v>108</v>
+      </c>
+      <c r="E24" t="s">
+        <v>109</v>
+      </c>
+      <c r="F24" t="s">
+        <v>21</v>
       </c>
       <c r="G24">
         <v>2400</v>
@@ -1442,11 +1933,11 @@
       <c r="J24">
         <v>52800</v>
       </c>
-      <c r="K24" t="str">
-        <v>2026-07-20</v>
-      </c>
-      <c r="L24" t="str">
-        <v>2026-08-12</v>
+      <c r="K24" t="s">
+        <v>110</v>
+      </c>
+      <c r="L24" t="s">
+        <v>111</v>
       </c>
       <c r="M24">
         <v>2</v>
@@ -1455,24 +1946,24 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="str">
-        <v/>
-      </c>
-      <c r="C25" t="str">
-        <v>4.3</v>
-      </c>
-      <c r="D25" t="str">
-        <v>Tarrajeo fino en cielorrasos y vigas</v>
-      </c>
-      <c r="E25" t="str">
-        <v>ARQ-ACAB-03</v>
-      </c>
-      <c r="F25" t="str">
-        <v>m2</v>
+      <c r="B25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" t="s">
+        <v>112</v>
+      </c>
+      <c r="D25" t="s">
+        <v>113</v>
+      </c>
+      <c r="E25" t="s">
+        <v>114</v>
+      </c>
+      <c r="F25" t="s">
+        <v>21</v>
       </c>
       <c r="G25">
         <v>850</v>
@@ -1486,11 +1977,11 @@
       <c r="J25">
         <v>22100</v>
       </c>
-      <c r="K25" t="str">
-        <v>2026-07-22</v>
-      </c>
-      <c r="L25" t="str">
-        <v>2026-08-15</v>
+      <c r="K25" t="s">
+        <v>115</v>
+      </c>
+      <c r="L25" t="s">
+        <v>116</v>
       </c>
       <c r="M25">
         <v>2</v>
@@ -1499,24 +1990,24 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="str">
-        <v/>
-      </c>
-      <c r="C26" t="str">
-        <v>4.4</v>
-      </c>
-      <c r="D26" t="str">
-        <v>Contrapiso de concreto e=2" en ambientes</v>
-      </c>
-      <c r="E26" t="str">
-        <v>ARQ-ACAB-04</v>
-      </c>
-      <c r="F26" t="str">
-        <v>m2</v>
+      <c r="B26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" t="s">
+        <v>117</v>
+      </c>
+      <c r="D26" t="s">
+        <v>118</v>
+      </c>
+      <c r="E26" t="s">
+        <v>119</v>
+      </c>
+      <c r="F26" t="s">
+        <v>21</v>
       </c>
       <c r="G26">
         <v>850</v>
@@ -1530,11 +2021,11 @@
       <c r="J26">
         <v>20400</v>
       </c>
-      <c r="K26" t="str">
-        <v>2026-07-28</v>
-      </c>
-      <c r="L26" t="str">
-        <v>2026-08-18</v>
+      <c r="K26" t="s">
+        <v>90</v>
+      </c>
+      <c r="L26" t="s">
+        <v>120</v>
       </c>
       <c r="M26">
         <v>2</v>
@@ -1543,24 +2034,24 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="str">
-        <v/>
-      </c>
-      <c r="C27" t="str">
-        <v>4.5</v>
-      </c>
-      <c r="D27" t="str">
-        <v>Instalación de piso porcelanato pulido 60x60</v>
-      </c>
-      <c r="E27" t="str">
-        <v>ARQ-ACAB-05</v>
-      </c>
-      <c r="F27" t="str">
-        <v>m2</v>
+      <c r="B27" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" t="s">
+        <v>121</v>
+      </c>
+      <c r="D27" t="s">
+        <v>122</v>
+      </c>
+      <c r="E27" t="s">
+        <v>123</v>
+      </c>
+      <c r="F27" t="s">
+        <v>21</v>
       </c>
       <c r="G27">
         <v>800</v>
@@ -1574,11 +2065,11 @@
       <c r="J27">
         <v>68000</v>
       </c>
-      <c r="K27" t="str">
-        <v>2026-08-01</v>
-      </c>
-      <c r="L27" t="str">
-        <v>2026-08-22</v>
+      <c r="K27" t="s">
+        <v>124</v>
+      </c>
+      <c r="L27" t="s">
+        <v>125</v>
       </c>
       <c r="M27">
         <v>2</v>
@@ -1587,24 +2078,24 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="str">
-        <v/>
-      </c>
-      <c r="C28" t="str">
-        <v>4.6</v>
-      </c>
-      <c r="D28" t="str">
-        <v>Pintura látex en muros interiores y columnas</v>
-      </c>
-      <c r="E28" t="str">
-        <v>ARQ-ACAB-06</v>
-      </c>
-      <c r="F28" t="str">
-        <v>m2</v>
+      <c r="B28" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" t="s">
+        <v>126</v>
+      </c>
+      <c r="D28" t="s">
+        <v>127</v>
+      </c>
+      <c r="E28" t="s">
+        <v>128</v>
+      </c>
+      <c r="F28" t="s">
+        <v>21</v>
       </c>
       <c r="G28">
         <v>2400</v>
@@ -1618,11 +2109,11 @@
       <c r="J28">
         <v>28800</v>
       </c>
-      <c r="K28" t="str">
-        <v>2026-08-10</v>
-      </c>
-      <c r="L28" t="str">
-        <v>2026-08-25</v>
+      <c r="K28" t="s">
+        <v>129</v>
+      </c>
+      <c r="L28" t="s">
+        <v>130</v>
       </c>
       <c r="M28">
         <v>2</v>
@@ -1631,24 +2122,24 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="str">
-        <v/>
-      </c>
-      <c r="C29" t="str">
-        <v>4.7</v>
-      </c>
-      <c r="D29" t="str">
-        <v>Puertas de madera contraplacada con cerraduras</v>
-      </c>
-      <c r="E29" t="str">
-        <v>ARQ-ACAB-07</v>
-      </c>
-      <c r="F29" t="str">
-        <v>und</v>
+      <c r="B29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" t="s">
+        <v>131</v>
+      </c>
+      <c r="D29" t="s">
+        <v>132</v>
+      </c>
+      <c r="E29" t="s">
+        <v>133</v>
+      </c>
+      <c r="F29" t="s">
+        <v>134</v>
       </c>
       <c r="G29">
         <v>32</v>
@@ -1662,11 +2153,11 @@
       <c r="J29">
         <v>14400</v>
       </c>
-      <c r="K29" t="str">
-        <v>2026-08-08</v>
-      </c>
-      <c r="L29" t="str">
-        <v>2026-08-20</v>
+      <c r="K29" t="s">
+        <v>135</v>
+      </c>
+      <c r="L29" t="s">
+        <v>136</v>
       </c>
       <c r="M29">
         <v>2</v>
@@ -1675,24 +2166,24 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="str">
-        <v/>
-      </c>
-      <c r="C30" t="str">
-        <v>4.8</v>
-      </c>
-      <c r="D30" t="str">
-        <v>Ventanas de vidrio templado templado e=8mm</v>
-      </c>
-      <c r="E30" t="str">
-        <v>ARQ-ACAB-08</v>
-      </c>
-      <c r="F30" t="str">
-        <v>m2</v>
+      <c r="B30" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" t="s">
+        <v>137</v>
+      </c>
+      <c r="D30" t="s">
+        <v>138</v>
+      </c>
+      <c r="E30" t="s">
+        <v>139</v>
+      </c>
+      <c r="F30" t="s">
+        <v>21</v>
       </c>
       <c r="G30">
         <v>110</v>
@@ -1706,11 +2197,11 @@
       <c r="J30">
         <v>24200</v>
       </c>
-      <c r="K30" t="str">
-        <v>2026-08-12</v>
-      </c>
-      <c r="L30" t="str">
-        <v>2026-08-24</v>
+      <c r="K30" t="s">
+        <v>111</v>
+      </c>
+      <c r="L30" t="s">
+        <v>140</v>
       </c>
       <c r="M30">
         <v>2</v>
@@ -1719,68 +2210,68 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="str">
-        <v>Instalaciones Sanitarias y Eléctricas</v>
-      </c>
-      <c r="C31" t="str">
-        <v/>
-      </c>
-      <c r="D31" t="str">
-        <v/>
-      </c>
-      <c r="E31" t="str">
-        <v>INS-SAN</v>
-      </c>
-      <c r="F31" t="str">
-        <v>Global</v>
-      </c>
-      <c r="G31" t="str">
-        <v/>
-      </c>
-      <c r="H31" t="str">
-        <v/>
-      </c>
-      <c r="I31" t="str">
-        <v/>
+      <c r="B31" t="s">
+        <v>141</v>
+      </c>
+      <c r="C31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31" t="s">
+        <v>142</v>
+      </c>
+      <c r="F31" t="s">
+        <v>17</v>
+      </c>
+      <c r="G31" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" t="s">
+        <v>15</v>
       </c>
       <c r="J31">
         <v>81590</v>
       </c>
-      <c r="K31" t="str">
-        <v/>
-      </c>
-      <c r="L31" t="str">
-        <v/>
+      <c r="K31" t="s">
+        <v>15</v>
+      </c>
+      <c r="L31" t="s">
+        <v>15</v>
       </c>
       <c r="M31">
         <v>1</v>
       </c>
-      <c r="N31" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="32">
+      <c r="N31" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" t="str">
-        <v/>
-      </c>
-      <c r="C32" t="str">
-        <v>5.1</v>
-      </c>
-      <c r="D32" t="str">
-        <v>Redes de desagüe y ventilación PVC de 4"</v>
-      </c>
-      <c r="E32" t="str">
-        <v>INS-SAN-01</v>
-      </c>
-      <c r="F32" t="str">
-        <v>m</v>
+      <c r="B32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" t="s">
+        <v>143</v>
+      </c>
+      <c r="D32" t="s">
+        <v>144</v>
+      </c>
+      <c r="E32" t="s">
+        <v>145</v>
+      </c>
+      <c r="F32" t="s">
+        <v>32</v>
       </c>
       <c r="G32">
         <v>320</v>
@@ -1794,11 +2285,11 @@
       <c r="J32">
         <v>13440</v>
       </c>
-      <c r="K32" t="str">
-        <v>2026-07-20</v>
-      </c>
-      <c r="L32" t="str">
-        <v>2026-08-10</v>
+      <c r="K32" t="s">
+        <v>110</v>
+      </c>
+      <c r="L32" t="s">
+        <v>129</v>
       </c>
       <c r="M32">
         <v>2</v>
@@ -1807,24 +2298,24 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" t="str">
-        <v/>
-      </c>
-      <c r="C33" t="str">
-        <v>5.2</v>
-      </c>
-      <c r="D33" t="str">
-        <v>Tendido de tubería de agua fría y caliente PVC</v>
-      </c>
-      <c r="E33" t="str">
-        <v>INS-SAN-02</v>
-      </c>
-      <c r="F33" t="str">
-        <v>m</v>
+      <c r="B33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" t="s">
+        <v>146</v>
+      </c>
+      <c r="D33" t="s">
+        <v>147</v>
+      </c>
+      <c r="E33" t="s">
+        <v>148</v>
+      </c>
+      <c r="F33" t="s">
+        <v>32</v>
       </c>
       <c r="G33">
         <v>450</v>
@@ -1838,11 +2329,11 @@
       <c r="J33">
         <v>15750</v>
       </c>
-      <c r="K33" t="str">
-        <v>2026-07-25</v>
-      </c>
-      <c r="L33" t="str">
-        <v>2026-08-15</v>
+      <c r="K33" t="s">
+        <v>149</v>
+      </c>
+      <c r="L33" t="s">
+        <v>116</v>
       </c>
       <c r="M33">
         <v>2</v>
@@ -1851,24 +2342,24 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" t="str">
-        <v/>
-      </c>
-      <c r="C34" t="str">
-        <v>5.3</v>
-      </c>
-      <c r="D34" t="str">
-        <v>Tuberías PVC de luz empotradas en losa/muros</v>
-      </c>
-      <c r="E34" t="str">
-        <v>INS-SAN-03</v>
-      </c>
-      <c r="F34" t="str">
-        <v>m</v>
+      <c r="B34" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" t="s">
+        <v>150</v>
+      </c>
+      <c r="D34" t="s">
+        <v>151</v>
+      </c>
+      <c r="E34" t="s">
+        <v>152</v>
+      </c>
+      <c r="F34" t="s">
+        <v>32</v>
       </c>
       <c r="G34">
         <v>950</v>
@@ -1882,11 +2373,11 @@
       <c r="J34">
         <v>17100</v>
       </c>
-      <c r="K34" t="str">
-        <v>2026-07-22</v>
-      </c>
-      <c r="L34" t="str">
-        <v>2026-08-12</v>
+      <c r="K34" t="s">
+        <v>115</v>
+      </c>
+      <c r="L34" t="s">
+        <v>111</v>
       </c>
       <c r="M34">
         <v>2</v>
@@ -1895,24 +2386,24 @@
         <v>30</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" t="str">
-        <v/>
-      </c>
-      <c r="C35" t="str">
-        <v>5.4</v>
-      </c>
-      <c r="D35" t="str">
-        <v>Cableado eléctrico de cobre tipo NH-80</v>
-      </c>
-      <c r="E35" t="str">
-        <v>INS-SAN-04</v>
-      </c>
-      <c r="F35" t="str">
-        <v>m</v>
+      <c r="B35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" t="s">
+        <v>153</v>
+      </c>
+      <c r="D35" t="s">
+        <v>154</v>
+      </c>
+      <c r="E35" t="s">
+        <v>155</v>
+      </c>
+      <c r="F35" t="s">
+        <v>32</v>
       </c>
       <c r="G35">
         <v>2800</v>
@@ -1926,11 +2417,11 @@
       <c r="J35">
         <v>18200</v>
       </c>
-      <c r="K35" t="str">
-        <v>2026-08-05</v>
-      </c>
-      <c r="L35" t="str">
-        <v>2026-08-22</v>
+      <c r="K35" t="s">
+        <v>106</v>
+      </c>
+      <c r="L35" t="s">
+        <v>125</v>
       </c>
       <c r="M35">
         <v>2</v>
@@ -1939,24 +2430,24 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" t="str">
-        <v/>
-      </c>
-      <c r="C36" t="str">
-        <v>5.5</v>
-      </c>
-      <c r="D36" t="str">
-        <v>Montaje de aparatos sanitarios y grifería</v>
-      </c>
-      <c r="E36" t="str">
-        <v>INS-SAN-05</v>
-      </c>
-      <c r="F36" t="str">
-        <v>jgo</v>
+      <c r="B36" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" t="s">
+        <v>156</v>
+      </c>
+      <c r="D36" t="s">
+        <v>157</v>
+      </c>
+      <c r="E36" t="s">
+        <v>158</v>
+      </c>
+      <c r="F36" t="s">
+        <v>159</v>
       </c>
       <c r="G36">
         <v>18</v>
@@ -1970,11 +2461,11 @@
       <c r="J36">
         <v>17100</v>
       </c>
-      <c r="K36" t="str">
-        <v>2026-08-18</v>
-      </c>
-      <c r="L36" t="str">
-        <v>2026-08-29</v>
+      <c r="K36" t="s">
+        <v>120</v>
+      </c>
+      <c r="L36" t="s">
+        <v>160</v>
       </c>
       <c r="M36">
         <v>2</v>
@@ -1984,8 +2475,9 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N36"/>
+    <ignoredError sqref="A1:N36" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>